--- a/reports/播客监控日报_2026-03-18.xlsx
+++ b/reports/播客监控日报_2026-03-18.xlsx
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1571604</v>
+        <v>1571686</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -555,7 +555,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>393273</t>
+          <t>393749</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>4545</t>
+          <t>4548</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>9189</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:57:55</t>
+          <t>2026-03-18 05:38:21</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>733326</v>
+        <v>733346</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>33174</t>
+          <t>33309</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>147</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:57:35</t>
+          <t>2026-03-18 05:38:01</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>531179</v>
+        <v>531219</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -685,27 +685,27 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>12994</t>
+          <t>13450</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>114</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>147</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:57:39</t>
+          <t>2026-03-18 05:38:05</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>356877</v>
+        <v>356944</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -750,17 +750,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31550</t>
+          <t>31637</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>157</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>144</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>384</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:57:41</t>
+          <t>2026-03-18 05:38:07</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>173719</v>
+        <v>173729</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11927</t>
+          <t>12002</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:56:39</t>
+          <t>2026-03-18 05:37:05</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>146044</v>
+        <v>146078</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3700</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:57:31</t>
+          <t>2026-03-18 05:37:57</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>141724</v>
+        <v>141731</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>18962</t>
+          <t>19079</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>192</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:57:43</t>
+          <t>2026-03-18 05:38:09</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>122515</v>
+        <v>122529</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12130</t>
+          <t>12198</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>109</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1040,14 +1040,14 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:57:27</t>
+          <t>2026-03-18 05:37:53</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>投资ABC｜掌握投资中那些绕不开的知识</t>
+          <t>听懂涨声</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1057,192 +1057,192 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>有知有行</t>
+          <t>天楠</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>94502</v>
+        <v>120371</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>低利率时代，我的定期存款到期了，这笔钱该怎么办？｜我问陈博士 14</t>
+          <t>40 岁的爸爸不上班，房子和孩子还得管 ｜ 红火开麦日</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12633</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>98</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>157</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47:21</t>
+          <t>55:56</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:57:37</t>
+          <t>2026-03-18 05:38:19</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>中欧基金</t>
+          <t>投资ABC｜掌握投资中那些绕不开的知识</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>公募基金</t>
+          <t>独立节目</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>中欧基金</t>
+          <t>有知有行</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>78777</v>
+        <v>94511</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46.HALO交易爆火：当AI狂奔，市场又开始拥抱“老派”资产</t>
+          <t>低利率时代，我的定期存款到期了，这笔钱该怎么办？｜我问陈博士 14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11243</t>
+          <t>12696</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>135</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26:25</t>
+          <t>47:21</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:56:41</t>
+          <t>2026-03-18 05:38:03</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>钱粮胡同FM</t>
+          <t>中欧基金</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>独立节目</t>
+          <t>公募基金</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>住在胡同的野人、无聊D、细菌佛</t>
+          <t>中欧基金</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>74806</v>
+        <v>78796</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>318.伊朗的昨天</t>
+          <t>46.HALO交易爆火：当AI狂奔，市场又开始拥抱“老派”资产</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>22799</t>
+          <t>11259</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>78</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>123</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1:54:25</t>
+          <t>26:25</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:57:49</t>
+          <t>2026-03-18 05:37:07</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>十分吸引</t>
+          <t>钱粮胡同FM</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1252,127 +1252,127 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>石磊</t>
+          <t>住在胡同的野人、无聊D、细菌佛</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>70483</v>
+        <v>74810</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Vol.59 当"失去的30年"叙事终结：我们该如何看待今天的日本？</t>
+          <t>318.伊朗的昨天</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17936</t>
+          <t>22938</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>177</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1:11:36</t>
+          <t>1:54:25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:57:47</t>
+          <t>2026-03-18 05:38:15</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>和盘托出</t>
+          <t>十分吸引</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>公募基金</t>
+          <t>独立节目</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>蚂蚁财富</t>
+          <t>石磊</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>49617</v>
+        <v>70500</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>关于马斯克精心布局，终于把"奇点年"召唤到眼前，这件大事</t>
+          <t>Vol.59 当"失去的30年"叙事终结：我们该如何看待今天的日本？</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>18096</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>82</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>174</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>254</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1:12:04</t>
+          <t>1:11:36</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:57:25</t>
+          <t>2026-03-18 05:38:13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>有富同享</t>
+          <t>和盘托出</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1382,192 +1382,192 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>富国基金</t>
+          <t>蚂蚁财富</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>38545</v>
+        <v>49617</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>一周富盘丨布伦特原油期货再度拉涨，伦敦金现货集体跳水，黄金避险人设崩塌？</t>
+          <t>关于马斯克精心布局，终于把"奇点年"召唤到眼前，这件大事</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>7674</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>75</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9:11</t>
+          <t>1:12:04</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:56:43</t>
+          <t>2026-03-18 05:37:51</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>The Wanderers 流浪者</t>
+          <t>有富同享</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>独立节目</t>
+          <t>公募基金</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>zjyiran、Jason_NDV、Vincent-Lu</t>
+          <t>富国基金</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>32150</v>
+        <v>38551</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2028智能危机：人类经济体会崩溃吗？</t>
+          <t>一周富盘丨布伦特原油期货再度拉涨，伦敦金现货集体跳水，黄金避险人设崩塌？</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19424</t>
+          <t>992</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1:13:53</t>
+          <t>9:11</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:57:45</t>
+          <t>2026-03-18 05:37:09</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>人间钱话</t>
+          <t>The Wanderers 流浪者</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>公募基金</t>
+          <t>独立节目</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>天弘基金</t>
+          <t>zjyiran、Jason_NDV、Vincent-Lu</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>26915</v>
+        <v>32150</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>E35 美伊冲突全球动荡，如何防止钱包烧毁？</t>
+          <t>2028智能危机：人类经济体会崩溃吗？</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2973</t>
+          <t>19435</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>129</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>131</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>215</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33:36</t>
+          <t>1:13:53</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:56:47</t>
+          <t>2026-03-18 05:38:11</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>泰度Voice</t>
+          <t>人间钱话</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1577,62 +1577,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>华泰证券</t>
+          <t>天弘基金</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>22736</v>
+        <v>26915</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>S3E11 | 超越传统“因子工厂”：AGI开启量化投资新时代</t>
+          <t>E35 美伊冲突全球动荡，如何防止钱包烧毁？</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>2984</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1:00:39</t>
+          <t>33:36</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:57:23</t>
+          <t>2026-03-18 05:37:13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>深度求真</t>
+          <t>泰度Voice</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1642,192 +1642,192 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>大成基金</t>
+          <t>华泰证券</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>20531</v>
+        <v>22736</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18.Seedance出炉，AI视频革命与科技投资新范式</t>
+          <t>S3E11 | 超越传统“因子工厂”：AGI开启量化投资新时代</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7651</t>
+          <t>955</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44:50</t>
+          <t>1:00:39</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:56:49</t>
+          <t>2026-03-18 05:37:49</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>燕妮聊基金</t>
+          <t>深度求真</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>独立节目</t>
+          <t>公募基金</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>燕妮</t>
+          <t>大成基金</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>17431</v>
+        <v>20531</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>87、聊聊那些投资迷思</t>
+          <t>18.Seedance出炉，AI视频革命与科技投资新范式</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>7651</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>176</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>133</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>309</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1:02:01</t>
+          <t>44:50</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:57:51</t>
+          <t>2026-03-18 05:37:15</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>话中有金</t>
+          <t>燕妮聊基金</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>公募基金</t>
+          <t>独立节目</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>中金资管</t>
+          <t>燕妮</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>8968</v>
+        <v>17431</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>EP135 对话中金公司食品饮料行业首席分析师：当“反向过年”遇上“下沉消费”</t>
+          <t>87、聊聊那些投资迷思</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>59:51</t>
+          <t>1:02:01</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:57:21</t>
+          <t>2026-03-18 05:38:17</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>德邦基金财经列车</t>
+          <t>话中有金</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>德邦基金</t>
+          <t>中金资管</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>8493</v>
+        <v>8969</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>311.3月17日财经速递</t>
+          <t>EP135 对话中金公司食品饮料行业首席分析师：当“反向过年”遇上“下沉消费”</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4:14</t>
+          <t>59:51</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:56:59</t>
+          <t>2026-03-18 05:37:47</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>随基漫步 Random Walk</t>
+          <t>德邦基金财经列车</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1902,25 +1902,25 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>兴全基金</t>
+          <t>德邦基金</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6998</v>
+        <v>8493</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>OpenClaw爆火后，AI发展的2个重点方向</t>
+          <t>311.3月17日财经速递</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>179</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1930,34 +1930,34 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>55:15</t>
+          <t>4:14</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:57:17</t>
+          <t>2026-03-18 05:37:25</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>茶水间经济学</t>
+          <t>随基漫步 Random Walk</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1967,62 +1967,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>易方达基金</t>
+          <t>兴全基金</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>6839</v>
+        <v>6999</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>对话三点下班浩哥：他说感谢股市改写了他的人生</t>
+          <t>OpenClaw爆火后，AI发展的2个重点方向</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1:42:13</t>
+          <t>55:15</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:57:09</t>
+          <t>2026-03-18 05:37:43</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>泰客Talk</t>
+          <t>茶水间经济学</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2032,62 +2032,62 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>国泰基金</t>
+          <t>易方达基金</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>6283</v>
+        <v>6839</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Vol 27 Z世代的新年消费回忆录</t>
+          <t>对话三点下班浩哥：他说感谢股市改写了他的人生</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>3214</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>27</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>53:31</t>
+          <t>1:42:13</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:57:07</t>
+          <t>2026-03-18 05:37:35</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>时间嘉讲</t>
+          <t>泰客Talk</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -2097,62 +2097,62 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>嘉实基金</t>
+          <t>国泰基金</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>5406</v>
+        <v>6283</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Ep10.当“一盒内存条=一套房”：这轮半导体行情谁在定价？</t>
+          <t>Vol 27 Z世代的新年消费回忆录</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>26466</t>
+          <t>4431</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>158</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>215</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1:20:43</t>
+          <t>53:31</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:57:05</t>
+          <t>2026-03-18 05:37:33</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>莫问钱程</t>
+          <t>时间嘉讲</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -2162,62 +2162,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>银华基金</t>
+          <t>嘉实基金</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>4481</v>
+        <v>5406</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>养娃这条路，做好财务规划能省多少弯路？</t>
+          <t>Ep10.当“一盒内存条=一套房”：这轮半导体行情谁在定价？</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>26471</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>225</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>297</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>522</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1:12:50</t>
+          <t>1:20:43</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:57:11</t>
+          <t>2026-03-18 05:37:31</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>财话连篇</t>
+          <t>莫问钱程</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2227,62 +2227,62 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>易方达基金</t>
+          <t>银华基金</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3816</v>
+        <v>4481</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Vol.18 | 越南市场为何快速上涨？——基金经理越南调研感受</t>
+          <t>养娃这条路，做好财务规划能省多少弯路？</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>5360</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>94</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>25:02</t>
+          <t>1:12:50</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:57:13</t>
+          <t>2026-03-18 05:37:37</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>养基方程式</t>
+          <t>财话连篇</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2292,62 +2292,62 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>广发基金</t>
+          <t>易方达基金</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>3297</v>
+        <v>3816</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>港股科技风起，未来路在何方？| 串台「自由进度条」</t>
+          <t>Vol.18 | 越南市场为何快速上涨？——基金经理越南调研感受</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>36</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>55:16</t>
+          <t>25:02</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:56:51</t>
+          <t>2026-03-18 05:37:39</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>钱途规划局</t>
+          <t>养基方程式</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2357,62 +2357,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>汇添富基金</t>
+          <t>广发基金</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>1989</v>
+        <v>3297</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>E20“宠物理财”小课堂：养毛孩子，怎样花钱不心疼？</t>
+          <t>港股科技风起，未来路在何方？| 串台「自由进度条」</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>263</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>55:16</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:57:15</t>
+          <t>2026-03-18 05:37:17</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>好朋友的直播间</t>
+          <t>钱途规划局</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2422,30 +2422,30 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>中泰资管</t>
+          <t>汇添富基金</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>1603</v>
+        <v>1989</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>E33.田瑀｜研究不必设限，结论宁缺毋滥</t>
+          <t>E20“宠物理财”小课堂：养毛孩子，怎样花钱不心疼？</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>189</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -2455,29 +2455,29 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>32:01</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:56:57</t>
+          <t>2026-03-18 05:37:41</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>投资心得·基金聊天局</t>
+          <t>好朋友的直播间</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2487,25 +2487,25 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>国投瑞银基金</t>
+          <t>中泰资管</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>1497</v>
+        <v>1603</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>EP10.没有终点的修行：育儿与投资的无限游戏</t>
+          <t>E33.田瑀｜研究不必设限，结论宁缺毋滥</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>396</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2520,29 +2520,29 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1:24:36</t>
+          <t>32:01</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:57:01</t>
+          <t>2026-03-18 05:37:23</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>与财同行</t>
+          <t>投资心得·基金聊天局</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2552,25 +2552,25 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>财通基金</t>
+          <t>国投瑞银基金</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>1305</v>
+        <v>1497</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>一线基金经理闭门分享：AI、有色、出海……2026年的钱往哪里投？</t>
+          <t>EP10.没有终点的修行：育儿与投资的无限游戏</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>43</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2580,34 +2580,34 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1:29:38</t>
+          <t>1:24:36</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:56:45</t>
+          <t>2026-03-18 05:37:27</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>鹏然心动</t>
+          <t>与财同行</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2617,143 +2617,147 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>鹏华基金</t>
+          <t>财通基金</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>740</v>
+        <v>1305</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Vol 3：新消费浪潮，Z世代用"情绪货币"改写"商业规则"？|元气消费局</t>
+          <t>一线基金经理闭门分享：AI、有色、出海……2026年的钱往哪里投？</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>23</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>54:38</t>
+          <t>1:29:38</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:57:19</t>
+          <t>2026-03-18 05:37:11</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>对话金融人</t>
+          <t>鹏然心动</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>其他金融机构</t>
+          <t>公募基金</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>广发证券</t>
+          <t>鹏华基金</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>481</v>
-      </c>
-      <c r="E35" s="2" t="inlineStr"/>
-      <c r="F35" s="2" t="inlineStr"/>
+        <v>740</v>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Vol 3：新消费浪潮，Z世代用"情绪货币"改写"商业规则"？|元气消费局</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>129</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr"/>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>54:38</t>
+        </is>
+      </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:57:33</t>
+          <t>2026-03-18 05:37:45</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>解盘一刻</t>
+          <t>对话金融人</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>公募基金</t>
+          <t>其他金融机构</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>华夏基金</t>
+          <t>广发证券</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>417</v>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>A股开年连跌三周，春节行情还能期待吗？0122</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>2024-01-22</t>
-        </is>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2776,21 +2780,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>19:20</t>
-        </is>
-      </c>
+      <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:57:29</t>
+          <t>2026-03-18 05:37:59</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>基金经理一周论市</t>
+          <t>解盘一刻</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2800,25 +2800,25 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>银华基金</t>
+          <t>华夏基金</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>305</v>
+        <v>417</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Vol 53：银华王丽敏：“周期搭台，成长唱戏”或是未来一段时间A股的主旋律</t>
+          <t>A股开年连跌三周，春节行情还能期待吗？0122</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2024-01-22</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>134</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2843,19 +2843,19 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2:01</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:56:53</t>
+          <t>2026-03-18 05:37:55</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>好朋友</t>
+          <t>基金经理一周论市</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2865,35 +2865,35 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>中泰资管</t>
+          <t>银华基金</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>51</v>
+        <v>305</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Vol.5 不上班的日子，跑步、做饭、好好生活</t>
+          <t>Vol 53：银华王丽敏：“周期搭台，成长唱戏”或是未来一段时间A股的主旋律</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>56</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2903,24 +2903,24 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1:00:18</t>
+          <t>2:01</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:56:55</t>
+          <t>2026-03-18 05:37:19</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>投资心法</t>
+          <t>好朋友</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2930,35 +2930,35 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>国投瑞银基金</t>
+          <t>中泰资管</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>0010 段永平《波士堂》访谈：敢为天下后</t>
+          <t>Vol.5 不上班的日子，跑步、做饭、好好生活</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2968,44 +2968,52 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>1:00:18</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:57:03</t>
+          <t>2026-03-18 05:37:21</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>听懂掌声</t>
+          <t>投资心法</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>独立节目</t>
+          <t>公募基金</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>天楠</t>
+          <t>国投瑞银基金</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>0010 段永平《波士堂》访谈：敢为天下后</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3028,10 +3036,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 04:57:53</t>
+          <t>2026-03-18 05:37:29</t>
         </is>
       </c>
     </row>
